--- a/Bibsam_tidskriftslistor/scifree_data_rsc.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_rsc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_8A8355D3CADCAC7CDE32A3D7DD027E6962EED8DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6981CAF2-9CB3-40A3-ADFE-32C4EACE27CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1993816B-F0AC-4FBA-B11A-8F3F29B16281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="143">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -314,15 +314,6 @@
   </si>
   <si>
     <t>http://dx.doi.org/10.1039/2051-6355/2014</t>
-  </si>
-  <si>
-    <t>2515-4184</t>
-  </si>
-  <si>
-    <t>Molecular Omics</t>
-  </si>
-  <si>
-    <t>http://dx.doi.org/10.1039/2515-4184/2018</t>
   </si>
   <si>
     <t>2058-9689</t>
@@ -513,16 +504,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5937BC2-CB9A-4140-B713-621CEF137D76}" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0">
-  <autoFilter ref="A1:G38" xr:uid="{D5937BC2-CB9A-4140-B713-621CEF137D76}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1852EF24-FC32-4BED-BB20-F93B6169178F}" name="Table2" displayName="Table2" ref="A1:G37" totalsRowShown="0">
+  <autoFilter ref="A1:G37" xr:uid="{1852EF24-FC32-4BED-BB20-F93B6169178F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G37">
+    <sortCondition ref="D1:D37"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9B21152B-56D7-4087-A6F1-4AB455A6BDD6}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{C007C9FD-1B6D-4514-A1E0-29FC9C203164}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{BC9D926D-81A1-4ECA-B2EB-B41069EE245B}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{2C7A0535-4D2B-44D8-AD30-CECD786A224B}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{35037A2E-BE41-49B6-A885-9DDEAC0375C8}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{101B9A58-E036-4F1A-A0F8-8D45416EBB37}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{A2026059-6076-4602-9473-F43C824A5569}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{66281345-2BF6-4F32-AF62-BEB9DFA3C838}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{4C67F164-AC05-41C5-A182-961EE2D28EBF}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{A510D5C2-AE2B-4076-B5AB-1670877960DC}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{639EB695-4CD5-4900-BEFE-96ABAF4E75E2}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{9ADE45C9-B7B9-4E84-BFA2-B51E642A5CCB}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{DEED1FA0-C7B5-486F-86B7-3566B44A061F}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{366A6940-C3F4-4E10-90F7-2AEEBD16EDB0}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -790,8 +784,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D853A405-97C0-4EAA-BEFC-87771E0E3BA0}">
-  <dimension ref="A1:G38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6896489F-62A3-4B78-880A-7EC9CCA3645C}">
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -846,7 +840,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,7 +863,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -892,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -915,7 +909,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -938,7 +932,7 @@
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -961,7 +955,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -981,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1004,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1027,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1050,7 +1044,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1073,7 +1067,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1096,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1119,7 +1113,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,7 +1136,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1165,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1208,7 +1202,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1231,7 +1225,7 @@
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1254,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1277,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1300,7 +1294,7 @@
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1320,7 +1314,7 @@
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1343,7 +1337,7 @@
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1363,7 +1357,7 @@
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1373,17 +1367,20 @@
       <c r="B26" t="s">
         <v>101</v>
       </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1391,9 +1388,6 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" t="s">
         <v>105</v>
       </c>
       <c r="D27" t="s">
@@ -1406,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1416,17 +1410,20 @@
       <c r="B28" t="s">
         <v>108</v>
       </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1434,22 +1431,22 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1457,22 +1454,22 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1480,22 +1477,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1503,19 +1497,22 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1523,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
         <v>124</v>
@@ -1538,7 +1535,7 @@
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,9 +1545,6 @@
       <c r="B34" t="s">
         <v>127</v>
       </c>
-      <c r="C34" t="s">
-        <v>127</v>
-      </c>
       <c r="D34" t="s">
         <v>128</v>
       </c>
@@ -1561,7 +1555,7 @@
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,19 +1563,19 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1589,19 +1583,22 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>130</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1609,42 +1606,19 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
-      </c>
-      <c r="C37" t="s">
         <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
